--- a/astro-site/public/dl/ice-cream-shop-checklist-templates/08-ice-cream-parlor-opening-closing-checklist.xlsx
+++ b/astro-site/public/dl/ice-cream-shop-checklist-templates/08-ice-cream-parlor-opening-closing-checklist.xlsx
@@ -1370,7 +1370,7 @@
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>Dipping cabinets switched to service mode — they stay on overnight with product inside (details in file 01, Opening tab)</t>
+          <t>Dipping cabinets back in service mode — done FIRST THING on arrival (file 01, Opening tab), so the pans soften to scooping temp before the door opens; they stay on overnight with product inside</t>
         </is>
       </c>
       <c r="C20" s="19" t="inlineStr">
@@ -1759,13 +1759,13 @@
       <c r="G8" s="19" t="inlineStr"/>
       <c r="H8" s="20" t="inlineStr"/>
     </row>
-    <row r="9" ht="33.25" customHeight="1">
+    <row r="9" ht="47" customHeight="1">
       <c r="A9" s="17" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="18" t="inlineStr">
         <is>
-          <t>Put the night covers on the dipping cabinets: they stay ON, in storage mode</t>
+          <t>Put the night covers or lids on the dipping cabinets: they stay ON (night/storage setting only if your model has one, per the manufacturer)</t>
         </is>
       </c>
       <c r="C9" s="19" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>Log the closing temps: dipping cabinets already in storage mode (0 °F) and freezers (0 °F or below) — log reading: ____ °F</t>
+          <t>Log the closing temps: dipping cabinets (6–10 °F, or their night setting) and freezers (0 °F or below) — log reading: ____ °F</t>
         </is>
       </c>
       <c r="C10" s="19" t="inlineStr">
@@ -1871,13 +1871,13 @@
       <c r="G12" s="19" t="inlineStr"/>
       <c r="H12" s="20" t="inlineStr"/>
     </row>
-    <row r="13" ht="33.25" customHeight="1">
+    <row r="13" ht="47" customHeight="1">
       <c r="A13" s="17" t="n">
         <v>9</v>
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>Final safety check: gas off, water off, small appliances unplugged — never the freezers or dipping cabinets</t>
+          <t>Final safety check: gas appliances off (waffle irons, griddles) if any, dipper well tap off, small appliances unplugged — never the freezers or dipping cabinets</t>
         </is>
       </c>
       <c r="C13" s="19" t="inlineStr">
